--- a/output/pdf_financials_xlsx/FOMO.xlsx
+++ b/output/pdf_financials_xlsx/FOMO.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.141946</v>
+        <v>-0.141946</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.133327</v>
+        <v>-3.133327</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.141946</v>
+        <v>-0.141946</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.133327</v>
+        <v>-3.133327</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.141946</v>
+        <v>-0.141946</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.133327</v>
+        <v>-3.133327</v>
       </c>
     </row>
     <row r="24">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>31.33327</v>
+        <v>-31.33327</v>
       </c>
     </row>
     <row r="27">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.141946</v>
+        <v>-0.141946</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.133327</v>
+        <v>-3.133327</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.141946</v>
+        <v>-0.141946</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.133327</v>
+        <v>-3.133327</v>
       </c>
     </row>
     <row r="30">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.364931</v>
       </c>
     </row>
     <row r="93">
@@ -2492,7 +2492,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -3292,10 +3296,10 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.141946</v>
+        <v>-0.141946</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>3.133327</v>
+        <v>-3.133327</v>
       </c>
     </row>
     <row r="39">

--- a/output/pdf_financials_xlsx/FOMO.xlsx
+++ b/output/pdf_financials_xlsx/FOMO.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012445</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023397</v>
       </c>
     </row>
     <row r="13">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.141946</v>
+        <v>-0.129501</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.133327</v>
+        <v>-3.10993</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.141946</v>
+        <v>-0.129501</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.133327</v>
+        <v>-3.10993</v>
       </c>
     </row>
     <row r="30">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.7134160000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.305758</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.7134160000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.305758</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.7134160000000001</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.817509</v>
+        <v>0.511751</v>
       </c>
     </row>
     <row r="49">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
